--- a/volunteersync/test/e2e/reports/vulnerability_test_report.xlsx
+++ b/volunteersync/test/e2e/reports/vulnerability_test_report.xlsx
@@ -20,7 +20,7 @@
     <t>Generated At</t>
   </si>
   <si>
-    <t>23/7/2026, 10:29:45 am</t>
+    <t>25/7/2026, 9:30:30 pm</t>
   </si>
   <si>
     <t>Suite</t>
@@ -148,7 +148,7 @@
     <t>Hardcoded Supabase anon key found in main.dart source code</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.081Z</t>
+    <t>2026-07-25T16:00:19.819Z</t>
   </si>
   <si>
     <t>Vulnerability confirmed.</t>
@@ -171,7 +171,7 @@
     <t>No Data Exposure vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.129Z</t>
+    <t>2026-07-25T16:00:19.854Z</t>
   </si>
   <si>
     <t>Control active.</t>
@@ -194,7 +194,7 @@
     <t>No Access Control vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.142Z</t>
+    <t>2026-07-25T16:00:19.865Z</t>
   </si>
   <si>
     <t>LND-VULN-04</t>
@@ -214,7 +214,7 @@
     <t>No Config Error vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.152Z</t>
+    <t>2026-07-25T16:00:19.874Z</t>
   </si>
   <si>
     <t>LND-VULN-05</t>
@@ -231,7 +231,7 @@
     <t>No Rate Limiting vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.165Z</t>
+    <t>2026-07-25T16:00:19.882Z</t>
   </si>
   <si>
     <t>LND-VULN-06</t>
@@ -248,7 +248,7 @@
     <t>No Client Logic vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.177Z</t>
+    <t>2026-07-25T16:00:19.888Z</t>
   </si>
   <si>
     <t>LND-VULN-07</t>
@@ -265,7 +265,7 @@
     <t>No Injection vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.187Z</t>
+    <t>2026-07-25T16:00:19.895Z</t>
   </si>
   <si>
     <t>LND-VULN-08</t>
@@ -282,7 +282,7 @@
     <t>No Broken Auth vulnerabilities found. Sanity checks passed.</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.201Z</t>
+    <t>2026-07-25T16:00:19.905Z</t>
   </si>
   <si>
     <t>LND-VULN-09</t>
@@ -291,7 +291,7 @@
     <t>Verify Landing screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.214Z</t>
+    <t>2026-07-25T16:00:19.914Z</t>
   </si>
   <si>
     <t>LND-VULN-10</t>
@@ -300,7 +300,7 @@
     <t>Verify Landing screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.223Z</t>
+    <t>2026-07-25T16:00:19.920Z</t>
   </si>
   <si>
     <t>LND-VULN-11</t>
@@ -309,7 +309,7 @@
     <t>Verify Landing screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.234Z</t>
+    <t>2026-07-25T16:00:19.927Z</t>
   </si>
   <si>
     <t>LND-VULN-12</t>
@@ -318,7 +318,7 @@
     <t>Verify Landing screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.246Z</t>
+    <t>2026-07-25T16:00:19.938Z</t>
   </si>
   <si>
     <t>LND-VULN-13</t>
@@ -327,7 +327,7 @@
     <t>Verify Landing screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.254Z</t>
+    <t>2026-07-25T16:00:19.944Z</t>
   </si>
   <si>
     <t>LND-VULN-14</t>
@@ -336,7 +336,7 @@
     <t>Verify Landing screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.263Z</t>
+    <t>2026-07-25T16:00:19.951Z</t>
   </si>
   <si>
     <t>LND-VULN-15</t>
@@ -345,7 +345,7 @@
     <t>Verify Landing screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.272Z</t>
+    <t>2026-07-25T16:00:19.957Z</t>
   </si>
   <si>
     <t>LND-VULN-16</t>
@@ -354,7 +354,7 @@
     <t>Verify Landing screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.283Z</t>
+    <t>2026-07-25T16:00:19.968Z</t>
   </si>
   <si>
     <t>LND-VULN-17</t>
@@ -363,7 +363,7 @@
     <t>Verify Landing screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.294Z</t>
+    <t>2026-07-25T16:00:19.977Z</t>
   </si>
   <si>
     <t>LND-VULN-18</t>
@@ -372,7 +372,7 @@
     <t>Verify Landing screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.303Z</t>
+    <t>2026-07-25T16:00:19.983Z</t>
   </si>
   <si>
     <t>LND-VULN-19</t>
@@ -381,7 +381,7 @@
     <t>Verify Landing screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.316Z</t>
+    <t>2026-07-25T16:00:19.992Z</t>
   </si>
   <si>
     <t>LND-VULN-20</t>
@@ -390,7 +390,7 @@
     <t>Verify Landing screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.326Z</t>
+    <t>2026-07-25T16:00:20.001Z</t>
   </si>
   <si>
     <t>LND-VULN-21</t>
@@ -399,7 +399,7 @@
     <t>Verify Landing screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.337Z</t>
+    <t>2026-07-25T16:00:20.009Z</t>
   </si>
   <si>
     <t>LND-VULN-22</t>
@@ -408,7 +408,7 @@
     <t>Verify Landing screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.349Z</t>
+    <t>2026-07-25T16:00:20.018Z</t>
   </si>
   <si>
     <t>LND-VULN-23</t>
@@ -417,7 +417,7 @@
     <t>Verify Landing screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.359Z</t>
+    <t>2026-07-25T16:00:20.025Z</t>
   </si>
   <si>
     <t>LND-VULN-24</t>
@@ -426,7 +426,7 @@
     <t>Verify Landing screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.368Z</t>
+    <t>2026-07-25T16:00:20.034Z</t>
   </si>
   <si>
     <t>LND-VULN-25</t>
@@ -435,7 +435,7 @@
     <t>Verify Landing screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.381Z</t>
+    <t>2026-07-25T16:00:20.044Z</t>
   </si>
   <si>
     <t>LND-VULN-26</t>
@@ -444,7 +444,7 @@
     <t>Verify Landing screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.391Z</t>
+    <t>2026-07-25T16:00:20.051Z</t>
   </si>
   <si>
     <t>LND-VULN-27</t>
@@ -453,7 +453,7 @@
     <t>Verify Landing screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.401Z</t>
+    <t>2026-07-25T16:00:20.060Z</t>
   </si>
   <si>
     <t>LND-VULN-28</t>
@@ -462,7 +462,7 @@
     <t>Verify Landing screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.411Z</t>
+    <t>2026-07-25T16:00:20.068Z</t>
   </si>
   <si>
     <t>LND-VULN-29</t>
@@ -471,7 +471,7 @@
     <t>Verify Landing screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.422Z</t>
+    <t>2026-07-25T16:00:20.077Z</t>
   </si>
   <si>
     <t>LND-VULN-30</t>
@@ -480,7 +480,7 @@
     <t>Verify Landing screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.433Z</t>
+    <t>2026-07-25T16:00:20.084Z</t>
   </si>
   <si>
     <t>LND-VULN-31</t>
@@ -489,7 +489,7 @@
     <t>Verify Landing screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.445Z</t>
+    <t>2026-07-25T16:00:20.093Z</t>
   </si>
   <si>
     <t>LND-VULN-32</t>
@@ -498,7 +498,7 @@
     <t>Verify Landing screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.458Z</t>
+    <t>2026-07-25T16:00:20.105Z</t>
   </si>
   <si>
     <t>LND-VULN-33</t>
@@ -507,7 +507,7 @@
     <t>Verify Landing screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.470Z</t>
+    <t>2026-07-25T16:00:20.113Z</t>
   </si>
   <si>
     <t>LND-VULN-34</t>
@@ -516,7 +516,7 @@
     <t>Verify Landing screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.484Z</t>
+    <t>2026-07-25T16:00:20.123Z</t>
   </si>
   <si>
     <t>LND-VULN-35</t>
@@ -525,7 +525,7 @@
     <t>Verify Landing screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.497Z</t>
+    <t>2026-07-25T16:00:20.133Z</t>
   </si>
   <si>
     <t>LND-VULN-36</t>
@@ -534,7 +534,7 @@
     <t>Verify Landing screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.508Z</t>
+    <t>2026-07-25T16:00:20.141Z</t>
   </si>
   <si>
     <t>LOG-VULN-01</t>
@@ -543,7 +543,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.519Z</t>
+    <t>2026-07-25T16:00:20.149Z</t>
   </si>
   <si>
     <t>LOG-VULN-02</t>
@@ -552,7 +552,7 @@
     <t>Verify Login screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.532Z</t>
+    <t>2026-07-25T16:00:20.166Z</t>
   </si>
   <si>
     <t>LOG-VULN-03</t>
@@ -561,7 +561,7 @@
     <t>Verify Login screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.544Z</t>
+    <t>2026-07-25T16:00:20.189Z</t>
   </si>
   <si>
     <t>LOG-VULN-04</t>
@@ -570,7 +570,7 @@
     <t>Verify Login screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.557Z</t>
+    <t>2026-07-25T16:00:20.212Z</t>
   </si>
   <si>
     <t>LOG-VULN-05</t>
@@ -579,7 +579,7 @@
     <t>Verify Login screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.570Z</t>
+    <t>2026-07-25T16:00:20.222Z</t>
   </si>
   <si>
     <t>LOG-VULN-06</t>
@@ -588,7 +588,7 @@
     <t>Verify Login screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.585Z</t>
+    <t>2026-07-25T16:00:20.248Z</t>
   </si>
   <si>
     <t>LOG-VULN-07</t>
@@ -597,7 +597,7 @@
     <t>Verify Login screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.597Z</t>
+    <t>2026-07-25T16:00:20.258Z</t>
   </si>
   <si>
     <t>LOG-VULN-08</t>
@@ -606,7 +606,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.613Z</t>
+    <t>2026-07-25T16:00:20.272Z</t>
   </si>
   <si>
     <t>LOG-VULN-09</t>
@@ -615,7 +615,7 @@
     <t>Verify Login screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.624Z</t>
+    <t>2026-07-25T16:00:20.280Z</t>
   </si>
   <si>
     <t>LOG-VULN-10</t>
@@ -630,7 +630,7 @@
     <t>Supabase session token stored in insecure local storage</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.636Z</t>
+    <t>2026-07-25T16:00:20.290Z</t>
   </si>
   <si>
     <t>LOG-VULN-11</t>
@@ -639,7 +639,7 @@
     <t>Verify Login screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.649Z</t>
+    <t>2026-07-25T16:00:20.301Z</t>
   </si>
   <si>
     <t>LOG-VULN-12</t>
@@ -648,7 +648,7 @@
     <t>Verify Login screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.665Z</t>
+    <t>2026-07-25T16:00:20.314Z</t>
   </si>
   <si>
     <t>LOG-VULN-13</t>
@@ -657,7 +657,7 @@
     <t>Verify Login screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.681Z</t>
+    <t>2026-07-25T16:00:20.324Z</t>
   </si>
   <si>
     <t>LOG-VULN-14</t>
@@ -666,7 +666,7 @@
     <t>Verify Login screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.699Z</t>
+    <t>2026-07-25T16:00:20.334Z</t>
   </si>
   <si>
     <t>LOG-VULN-15</t>
@@ -675,7 +675,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.716Z</t>
+    <t>2026-07-25T16:00:20.344Z</t>
   </si>
   <si>
     <t>LOG-VULN-16</t>
@@ -684,7 +684,7 @@
     <t>Verify Login screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.734Z</t>
+    <t>2026-07-25T16:00:20.355Z</t>
   </si>
   <si>
     <t>LOG-VULN-17</t>
@@ -693,7 +693,7 @@
     <t>Verify Login screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.752Z</t>
+    <t>2026-07-25T16:00:20.366Z</t>
   </si>
   <si>
     <t>LOG-VULN-18</t>
@@ -702,7 +702,7 @@
     <t>Verify Login screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.766Z</t>
+    <t>2026-07-25T16:00:20.377Z</t>
   </si>
   <si>
     <t>LOG-VULN-19</t>
@@ -711,7 +711,7 @@
     <t>Verify Login screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.780Z</t>
+    <t>2026-07-25T16:00:20.388Z</t>
   </si>
   <si>
     <t>LOG-VULN-20</t>
@@ -720,7 +720,7 @@
     <t>Verify Login screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.793Z</t>
+    <t>2026-07-25T16:00:20.398Z</t>
   </si>
   <si>
     <t>LOG-VULN-21</t>
@@ -729,7 +729,7 @@
     <t>Verify Login screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.807Z</t>
+    <t>2026-07-25T16:00:20.410Z</t>
   </si>
   <si>
     <t>LOG-VULN-22</t>
@@ -738,7 +738,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.821Z</t>
+    <t>2026-07-25T16:00:20.420Z</t>
   </si>
   <si>
     <t>LOG-VULN-23</t>
@@ -747,7 +747,7 @@
     <t>Verify Login screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.837Z</t>
+    <t>2026-07-25T16:00:20.432Z</t>
   </si>
   <si>
     <t>LOG-VULN-24</t>
@@ -756,7 +756,7 @@
     <t>Verify Login screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.851Z</t>
+    <t>2026-07-25T16:00:20.447Z</t>
   </si>
   <si>
     <t>LOG-VULN-25</t>
@@ -765,7 +765,7 @@
     <t>Verify Login screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.865Z</t>
+    <t>2026-07-25T16:00:20.457Z</t>
   </si>
   <si>
     <t>LOG-VULN-26</t>
@@ -774,7 +774,7 @@
     <t>Verify Login screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.883Z</t>
+    <t>2026-07-25T16:00:20.470Z</t>
   </si>
   <si>
     <t>LOG-VULN-27</t>
@@ -783,7 +783,7 @@
     <t>Verify Login screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.898Z</t>
+    <t>2026-07-25T16:00:20.484Z</t>
   </si>
   <si>
     <t>LOG-VULN-28</t>
@@ -792,7 +792,7 @@
     <t>Verify Login screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.914Z</t>
+    <t>2026-07-25T16:00:20.496Z</t>
   </si>
   <si>
     <t>LOG-VULN-29</t>
@@ -801,7 +801,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.930Z</t>
+    <t>2026-07-25T16:00:20.510Z</t>
   </si>
   <si>
     <t>LOG-VULN-30</t>
@@ -810,7 +810,7 @@
     <t>Verify Login screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.946Z</t>
+    <t>2026-07-25T16:00:20.522Z</t>
   </si>
   <si>
     <t>LOG-VULN-31</t>
@@ -819,7 +819,7 @@
     <t>Verify Login screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.963Z</t>
+    <t>2026-07-25T16:00:20.536Z</t>
   </si>
   <si>
     <t>LOG-VULN-32</t>
@@ -828,7 +828,7 @@
     <t>Verify Login screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:29.983Z</t>
+    <t>2026-07-25T16:00:20.546Z</t>
   </si>
   <si>
     <t>LOG-VULN-33</t>
@@ -837,7 +837,7 @@
     <t>Verify Login screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.000Z</t>
+    <t>2026-07-25T16:00:20.560Z</t>
   </si>
   <si>
     <t>LOG-VULN-34</t>
@@ -846,7 +846,7 @@
     <t>Verify Login screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.019Z</t>
+    <t>2026-07-25T16:00:20.573Z</t>
   </si>
   <si>
     <t>LOG-VULN-35</t>
@@ -855,7 +855,7 @@
     <t>Verify Login screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.036Z</t>
+    <t>2026-07-25T16:00:20.585Z</t>
   </si>
   <si>
     <t>LOG-VULN-36</t>
@@ -864,7 +864,7 @@
     <t>Verify Login screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.053Z</t>
+    <t>2026-07-25T16:00:20.596Z</t>
   </si>
   <si>
     <t>REG-VULN-01</t>
@@ -873,7 +873,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.072Z</t>
+    <t>2026-07-25T16:00:20.609Z</t>
   </si>
   <si>
     <t>REG-VULN-02</t>
@@ -882,7 +882,7 @@
     <t>Verify Register screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.091Z</t>
+    <t>2026-07-25T16:00:20.620Z</t>
   </si>
   <si>
     <t>REG-VULN-03</t>
@@ -891,7 +891,7 @@
     <t>Verify Register screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.109Z</t>
+    <t>2026-07-25T16:00:20.633Z</t>
   </si>
   <si>
     <t>REG-VULN-04</t>
@@ -900,7 +900,7 @@
     <t>Verify Register screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.127Z</t>
+    <t>2026-07-25T16:00:20.645Z</t>
   </si>
   <si>
     <t>REG-VULN-05</t>
@@ -915,7 +915,7 @@
     <t>Client role value (e.g. admin) trusted on registration</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.144Z</t>
+    <t>2026-07-25T16:00:20.658Z</t>
   </si>
   <si>
     <t>REG-VULN-06</t>
@@ -924,7 +924,7 @@
     <t>Verify Register screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.166Z</t>
+    <t>2026-07-25T16:00:20.670Z</t>
   </si>
   <si>
     <t>REG-VULN-07</t>
@@ -933,7 +933,7 @@
     <t>Verify Register screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.190Z</t>
+    <t>2026-07-25T16:00:20.684Z</t>
   </si>
   <si>
     <t>REG-VULN-08</t>
@@ -942,7 +942,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.211Z</t>
+    <t>2026-07-25T16:00:20.696Z</t>
   </si>
   <si>
     <t>REG-VULN-09</t>
@@ -951,7 +951,7 @@
     <t>Verify Register screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.231Z</t>
+    <t>2026-07-25T16:00:20.709Z</t>
   </si>
   <si>
     <t>REG-VULN-10</t>
@@ -960,7 +960,7 @@
     <t>Verify Register screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.252Z</t>
+    <t>2026-07-25T16:00:20.720Z</t>
   </si>
   <si>
     <t>REG-VULN-11</t>
@@ -969,7 +969,7 @@
     <t>Verify Register screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.270Z</t>
+    <t>2026-07-25T16:00:20.734Z</t>
   </si>
   <si>
     <t>REG-VULN-12</t>
@@ -978,7 +978,7 @@
     <t>Verify Register screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.294Z</t>
+    <t>2026-07-25T16:00:20.746Z</t>
   </si>
   <si>
     <t>REG-VULN-13</t>
@@ -987,7 +987,7 @@
     <t>Verify Register screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.316Z</t>
+    <t>2026-07-25T16:00:20.759Z</t>
   </si>
   <si>
     <t>REG-VULN-14</t>
@@ -996,7 +996,7 @@
     <t>Verify Register screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.338Z</t>
+    <t>2026-07-25T16:00:20.777Z</t>
   </si>
   <si>
     <t>REG-VULN-15</t>
@@ -1005,7 +1005,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.357Z</t>
+    <t>2026-07-25T16:00:20.790Z</t>
   </si>
   <si>
     <t>REG-VULN-16</t>
@@ -1014,7 +1014,7 @@
     <t>Verify Register screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.378Z</t>
+    <t>2026-07-25T16:00:20.825Z</t>
   </si>
   <si>
     <t>REG-VULN-17</t>
@@ -1023,7 +1023,7 @@
     <t>Verify Register screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.396Z</t>
+    <t>2026-07-25T16:00:20.840Z</t>
   </si>
   <si>
     <t>REG-VULN-18</t>
@@ -1032,7 +1032,7 @@
     <t>Verify Register screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.413Z</t>
+    <t>2026-07-25T16:00:20.853Z</t>
   </si>
   <si>
     <t>REG-VULN-19</t>
@@ -1041,7 +1041,7 @@
     <t>Verify Register screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.434Z</t>
+    <t>2026-07-25T16:00:20.865Z</t>
   </si>
   <si>
     <t>REG-VULN-20</t>
@@ -1050,7 +1050,7 @@
     <t>Verify Register screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.452Z</t>
+    <t>2026-07-25T16:00:20.882Z</t>
   </si>
   <si>
     <t>REG-VULN-21</t>
@@ -1059,7 +1059,7 @@
     <t>Verify Register screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.477Z</t>
+    <t>2026-07-25T16:00:20.896Z</t>
   </si>
   <si>
     <t>REG-VULN-22</t>
@@ -1068,7 +1068,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.498Z</t>
+    <t>2026-07-25T16:00:20.911Z</t>
   </si>
   <si>
     <t>REG-VULN-23</t>
@@ -1077,7 +1077,7 @@
     <t>Verify Register screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.516Z</t>
+    <t>2026-07-25T16:00:20.925Z</t>
   </si>
   <si>
     <t>REG-VULN-24</t>
@@ -1086,7 +1086,7 @@
     <t>Verify Register screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.536Z</t>
+    <t>2026-07-25T16:00:20.942Z</t>
   </si>
   <si>
     <t>REG-VULN-25</t>
@@ -1095,7 +1095,7 @@
     <t>Verify Register screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.560Z</t>
+    <t>2026-07-25T16:00:20.958Z</t>
   </si>
   <si>
     <t>REG-VULN-26</t>
@@ -1104,7 +1104,7 @@
     <t>Verify Register screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.590Z</t>
+    <t>2026-07-25T16:00:20.974Z</t>
   </si>
   <si>
     <t>REG-VULN-27</t>
@@ -1113,7 +1113,7 @@
     <t>Verify Register screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.614Z</t>
+    <t>2026-07-25T16:00:20.989Z</t>
   </si>
   <si>
     <t>REG-VULN-28</t>
@@ -1122,7 +1122,7 @@
     <t>Verify Register screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.636Z</t>
+    <t>2026-07-25T16:00:21.007Z</t>
   </si>
   <si>
     <t>REG-VULN-29</t>
@@ -1131,7 +1131,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.664Z</t>
+    <t>2026-07-25T16:00:21.024Z</t>
   </si>
   <si>
     <t>REG-VULN-30</t>
@@ -1140,7 +1140,7 @@
     <t>Verify Register screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.692Z</t>
+    <t>2026-07-25T16:00:21.042Z</t>
   </si>
   <si>
     <t>REG-VULN-31</t>
@@ -1149,7 +1149,7 @@
     <t>Verify Register screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.719Z</t>
+    <t>2026-07-25T16:00:21.056Z</t>
   </si>
   <si>
     <t>REG-VULN-32</t>
@@ -1158,7 +1158,7 @@
     <t>Verify Register screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.740Z</t>
+    <t>2026-07-25T16:00:21.073Z</t>
   </si>
   <si>
     <t>REG-VULN-33</t>
@@ -1167,7 +1167,7 @@
     <t>Verify Register screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.762Z</t>
+    <t>2026-07-25T16:00:21.088Z</t>
   </si>
   <si>
     <t>REG-VULN-34</t>
@@ -1176,7 +1176,7 @@
     <t>Verify Register screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.786Z</t>
+    <t>2026-07-25T16:00:21.105Z</t>
   </si>
   <si>
     <t>REG-VULN-35</t>
@@ -1185,7 +1185,7 @@
     <t>Verify Register screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.809Z</t>
+    <t>2026-07-25T16:00:21.122Z</t>
   </si>
   <si>
     <t>REG-VULN-36</t>
@@ -1194,7 +1194,7 @@
     <t>Verify Register screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.832Z</t>
+    <t>2026-07-25T16:00:21.138Z</t>
   </si>
   <si>
     <t>FP-VULN-01</t>
@@ -1203,7 +1203,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.855Z</t>
+    <t>2026-07-25T16:00:21.153Z</t>
   </si>
   <si>
     <t>FP-VULN-02</t>
@@ -1212,7 +1212,7 @@
     <t>Verify ForgotPassword screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.880Z</t>
+    <t>2026-07-25T16:00:21.169Z</t>
   </si>
   <si>
     <t>FP-VULN-03</t>
@@ -1221,7 +1221,7 @@
     <t>Verify ForgotPassword screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.903Z</t>
+    <t>2026-07-25T16:00:21.184Z</t>
   </si>
   <si>
     <t>FP-VULN-04</t>
@@ -1230,7 +1230,7 @@
     <t>Verify ForgotPassword screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.928Z</t>
+    <t>2026-07-25T16:00:21.201Z</t>
   </si>
   <si>
     <t>FP-VULN-05</t>
@@ -1239,7 +1239,7 @@
     <t>Verify ForgotPassword screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.954Z</t>
+    <t>2026-07-25T16:00:21.218Z</t>
   </si>
   <si>
     <t>FP-VULN-06</t>
@@ -1248,7 +1248,7 @@
     <t>Verify ForgotPassword screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:30.986Z</t>
+    <t>2026-07-25T16:00:21.236Z</t>
   </si>
   <si>
     <t>FP-VULN-07</t>
@@ -1257,7 +1257,7 @@
     <t>Verify ForgotPassword screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.019Z</t>
+    <t>2026-07-25T16:00:21.251Z</t>
   </si>
   <si>
     <t>FP-VULN-08</t>
@@ -1266,7 +1266,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.045Z</t>
+    <t>2026-07-25T16:00:21.270Z</t>
   </si>
   <si>
     <t>FP-VULN-09</t>
@@ -1275,7 +1275,7 @@
     <t>Verify ForgotPassword screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.067Z</t>
+    <t>2026-07-25T16:00:21.286Z</t>
   </si>
   <si>
     <t>FP-VULN-10</t>
@@ -1284,7 +1284,7 @@
     <t>Verify ForgotPassword screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.094Z</t>
+    <t>2026-07-25T16:00:21.306Z</t>
   </si>
   <si>
     <t>FP-VULN-11</t>
@@ -1293,7 +1293,7 @@
     <t>Verify ForgotPassword screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.128Z</t>
+    <t>2026-07-25T16:00:21.321Z</t>
   </si>
   <si>
     <t>FP-VULN-12</t>
@@ -1302,7 +1302,7 @@
     <t>Verify ForgotPassword screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.163Z</t>
+    <t>2026-07-25T16:00:21.342Z</t>
   </si>
   <si>
     <t>FP-VULN-13</t>
@@ -1311,7 +1311,7 @@
     <t>Verify ForgotPassword screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.193Z</t>
+    <t>2026-07-25T16:00:21.357Z</t>
   </si>
   <si>
     <t>FP-VULN-14</t>
@@ -1320,7 +1320,7 @@
     <t>Verify ForgotPassword screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.221Z</t>
+    <t>2026-07-25T16:00:21.376Z</t>
   </si>
   <si>
     <t>FP-VULN-15</t>
@@ -1329,7 +1329,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.251Z</t>
+    <t>2026-07-25T16:00:21.391Z</t>
   </si>
   <si>
     <t>FP-VULN-16</t>
@@ -1338,7 +1338,7 @@
     <t>Verify ForgotPassword screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.273Z</t>
+    <t>2026-07-25T16:00:21.410Z</t>
   </si>
   <si>
     <t>FP-VULN-17</t>
@@ -1347,7 +1347,7 @@
     <t>Verify ForgotPassword screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.307Z</t>
+    <t>2026-07-25T16:00:21.430Z</t>
   </si>
   <si>
     <t>FP-VULN-18</t>
@@ -1356,7 +1356,7 @@
     <t>Verify ForgotPassword screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.335Z</t>
+    <t>2026-07-25T16:00:21.450Z</t>
   </si>
   <si>
     <t>FP-VULN-19</t>
@@ -1365,7 +1365,7 @@
     <t>Verify ForgotPassword screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.371Z</t>
+    <t>2026-07-25T16:00:21.470Z</t>
   </si>
   <si>
     <t>FP-VULN-20</t>
@@ -1374,7 +1374,7 @@
     <t>Verify ForgotPassword screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.410Z</t>
+    <t>2026-07-25T16:00:21.486Z</t>
   </si>
   <si>
     <t>FP-VULN-21</t>
@@ -1383,7 +1383,7 @@
     <t>Verify ForgotPassword screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.442Z</t>
+    <t>2026-07-25T16:00:21.508Z</t>
   </si>
   <si>
     <t>FP-VULN-22</t>
@@ -1392,7 +1392,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.476Z</t>
+    <t>2026-07-25T16:00:21.524Z</t>
   </si>
   <si>
     <t>FP-VULN-23</t>
@@ -1401,7 +1401,7 @@
     <t>Verify ForgotPassword screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.501Z</t>
+    <t>2026-07-25T16:00:21.542Z</t>
   </si>
   <si>
     <t>FP-VULN-24</t>
@@ -1410,7 +1410,7 @@
     <t>Verify ForgotPassword screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.548Z</t>
+    <t>2026-07-25T16:00:21.561Z</t>
   </si>
   <si>
     <t>FP-VULN-25</t>
@@ -1419,7 +1419,7 @@
     <t>Verify ForgotPassword screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.585Z</t>
+    <t>2026-07-25T16:00:21.581Z</t>
   </si>
   <si>
     <t>FP-VULN-26</t>
@@ -1428,7 +1428,7 @@
     <t>Verify ForgotPassword screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.608Z</t>
+    <t>2026-07-25T16:00:21.602Z</t>
   </si>
   <si>
     <t>FP-VULN-27</t>
@@ -1437,7 +1437,7 @@
     <t>Verify ForgotPassword screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.636Z</t>
+    <t>2026-07-25T16:00:21.621Z</t>
   </si>
   <si>
     <t>FP-VULN-28</t>
@@ -1446,7 +1446,7 @@
     <t>Verify ForgotPassword screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.671Z</t>
+    <t>2026-07-25T16:00:21.642Z</t>
   </si>
   <si>
     <t>FP-VULN-29</t>
@@ -1455,7 +1455,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.701Z</t>
+    <t>2026-07-25T16:00:21.659Z</t>
   </si>
   <si>
     <t>FP-VULN-30</t>
@@ -1464,7 +1464,7 @@
     <t>Verify ForgotPassword screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.725Z</t>
+    <t>2026-07-25T16:00:21.678Z</t>
   </si>
   <si>
     <t>FP-VULN-31</t>
@@ -1473,7 +1473,7 @@
     <t>Verify ForgotPassword screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.751Z</t>
+    <t>2026-07-25T16:00:21.696Z</t>
   </si>
   <si>
     <t>FP-VULN-32</t>
@@ -1482,7 +1482,7 @@
     <t>Verify ForgotPassword screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.777Z</t>
+    <t>2026-07-25T16:00:21.716Z</t>
   </si>
   <si>
     <t>FP-VULN-33</t>
@@ -1491,7 +1491,7 @@
     <t>Verify ForgotPassword screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.806Z</t>
+    <t>2026-07-25T16:00:21.736Z</t>
   </si>
   <si>
     <t>FP-VULN-34</t>
@@ -1500,7 +1500,7 @@
     <t>Verify ForgotPassword screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.840Z</t>
+    <t>2026-07-25T16:00:21.755Z</t>
   </si>
   <si>
     <t>FP-VULN-35</t>
@@ -1509,7 +1509,7 @@
     <t>Verify ForgotPassword screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.880Z</t>
+    <t>2026-07-25T16:00:21.776Z</t>
   </si>
   <si>
     <t>FP-VULN-36</t>
@@ -1518,7 +1518,7 @@
     <t>Verify ForgotPassword screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.909Z</t>
+    <t>2026-07-25T16:00:21.796Z</t>
   </si>
   <si>
     <t>DASH-VULN-01</t>
@@ -1527,7 +1527,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.952Z</t>
+    <t>2026-07-25T16:00:21.819Z</t>
   </si>
   <si>
     <t>DASH-VULN-02</t>
@@ -1536,7 +1536,7 @@
     <t>Verify Dashboard screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:31.996Z</t>
+    <t>2026-07-25T16:00:21.839Z</t>
   </si>
   <si>
     <t>DASH-VULN-03</t>
@@ -1545,7 +1545,7 @@
     <t>Verify Dashboard screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.029Z</t>
+    <t>2026-07-25T16:00:21.857Z</t>
   </si>
   <si>
     <t>DASH-VULN-04</t>
@@ -1554,7 +1554,7 @@
     <t>Verify Dashboard screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.064Z</t>
+    <t>2026-07-25T16:00:21.880Z</t>
   </si>
   <si>
     <t>DASH-VULN-05</t>
@@ -1563,7 +1563,7 @@
     <t>Verify Dashboard screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.106Z</t>
+    <t>2026-07-25T16:00:21.898Z</t>
   </si>
   <si>
     <t>DASH-VULN-06</t>
@@ -1572,7 +1572,7 @@
     <t>Verify Dashboard screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.142Z</t>
+    <t>2026-07-25T16:00:21.921Z</t>
   </si>
   <si>
     <t>DASH-VULN-07</t>
@@ -1581,7 +1581,7 @@
     <t>Verify Dashboard screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.181Z</t>
+    <t>2026-07-25T16:00:21.942Z</t>
   </si>
   <si>
     <t>DASH-VULN-08</t>
@@ -1590,7 +1590,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.219Z</t>
+    <t>2026-07-25T16:00:21.961Z</t>
   </si>
   <si>
     <t>DASH-VULN-09</t>
@@ -1599,7 +1599,7 @@
     <t>Verify Dashboard screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.257Z</t>
+    <t>2026-07-25T16:00:21.982Z</t>
   </si>
   <si>
     <t>DASH-VULN-10</t>
@@ -1608,7 +1608,7 @@
     <t>Verify Dashboard screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.292Z</t>
+    <t>2026-07-25T16:00:22.005Z</t>
   </si>
   <si>
     <t>DASH-VULN-11</t>
@@ -1617,7 +1617,7 @@
     <t>Verify Dashboard screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.325Z</t>
+    <t>2026-07-25T16:00:22.023Z</t>
   </si>
   <si>
     <t>DASH-VULN-12</t>
@@ -1626,7 +1626,7 @@
     <t>Verify Dashboard screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.357Z</t>
+    <t>2026-07-25T16:00:22.042Z</t>
   </si>
   <si>
     <t>DASH-VULN-13</t>
@@ -1635,7 +1635,7 @@
     <t>Verify Dashboard screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.400Z</t>
+    <t>2026-07-25T16:00:22.064Z</t>
   </si>
   <si>
     <t>DASH-VULN-14</t>
@@ -1644,7 +1644,7 @@
     <t>Verify Dashboard screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.441Z</t>
+    <t>2026-07-25T16:00:22.086Z</t>
   </si>
   <si>
     <t>DASH-VULN-15</t>
@@ -1653,7 +1653,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.488Z</t>
+    <t>2026-07-25T16:00:22.113Z</t>
   </si>
   <si>
     <t>DASH-VULN-16</t>
@@ -1662,7 +1662,7 @@
     <t>Verify Dashboard screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.527Z</t>
+    <t>2026-07-25T16:00:22.134Z</t>
   </si>
   <si>
     <t>DASH-VULN-17</t>
@@ -1671,7 +1671,7 @@
     <t>Verify Dashboard screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.564Z</t>
+    <t>2026-07-25T16:00:22.183Z</t>
   </si>
   <si>
     <t>DASH-VULN-18</t>
@@ -1680,7 +1680,7 @@
     <t>Verify Dashboard screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.591Z</t>
+    <t>2026-07-25T16:00:22.216Z</t>
   </si>
   <si>
     <t>DASH-VULN-19</t>
@@ -1689,7 +1689,7 @@
     <t>Verify Dashboard screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.644Z</t>
+    <t>2026-07-25T16:00:22.238Z</t>
   </si>
   <si>
     <t>DASH-VULN-20</t>
@@ -1698,7 +1698,7 @@
     <t>Verify Dashboard screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.681Z</t>
+    <t>2026-07-25T16:00:22.259Z</t>
   </si>
   <si>
     <t>DASH-VULN-21</t>
@@ -1707,7 +1707,7 @@
     <t>Verify Dashboard screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.732Z</t>
+    <t>2026-07-25T16:00:22.282Z</t>
   </si>
   <si>
     <t>DASH-VULN-22</t>
@@ -1716,7 +1716,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.769Z</t>
+    <t>2026-07-25T16:00:22.308Z</t>
   </si>
   <si>
     <t>DASH-VULN-23</t>
@@ -1725,7 +1725,7 @@
     <t>Verify Dashboard screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.807Z</t>
+    <t>2026-07-25T16:00:22.328Z</t>
   </si>
   <si>
     <t>DASH-VULN-24</t>
@@ -1734,7 +1734,7 @@
     <t>Verify Dashboard screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.835Z</t>
+    <t>2026-07-25T16:00:22.350Z</t>
   </si>
   <si>
     <t>DASH-VULN-25</t>
@@ -1743,7 +1743,7 @@
     <t>Verify Dashboard screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.864Z</t>
+    <t>2026-07-25T16:00:22.373Z</t>
   </si>
   <si>
     <t>DASH-VULN-26</t>
@@ -1752,7 +1752,7 @@
     <t>Verify Dashboard screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.922Z</t>
+    <t>2026-07-25T16:00:22.396Z</t>
   </si>
   <si>
     <t>DASH-VULN-27</t>
@@ -1761,7 +1761,7 @@
     <t>Verify Dashboard screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:32.970Z</t>
+    <t>2026-07-25T16:00:22.417Z</t>
   </si>
   <si>
     <t>DASH-VULN-28</t>
@@ -1770,7 +1770,7 @@
     <t>Verify Dashboard screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.020Z</t>
+    <t>2026-07-25T16:00:22.440Z</t>
   </si>
   <si>
     <t>DASH-VULN-29</t>
@@ -1779,7 +1779,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.068Z</t>
+    <t>2026-07-25T16:00:22.463Z</t>
   </si>
   <si>
     <t>DASH-VULN-30</t>
@@ -1788,7 +1788,7 @@
     <t>Verify Dashboard screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.110Z</t>
+    <t>2026-07-25T16:00:22.486Z</t>
   </si>
   <si>
     <t>DASH-VULN-31</t>
@@ -1797,7 +1797,7 @@
     <t>Verify Dashboard screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.155Z</t>
+    <t>2026-07-25T16:00:22.510Z</t>
   </si>
   <si>
     <t>DASH-VULN-32</t>
@@ -1806,7 +1806,7 @@
     <t>Verify Dashboard screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.200Z</t>
+    <t>2026-07-25T16:00:22.536Z</t>
   </si>
   <si>
     <t>DASH-VULN-33</t>
@@ -1815,7 +1815,7 @@
     <t>Verify Dashboard screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.230Z</t>
+    <t>2026-07-25T16:00:22.557Z</t>
   </si>
   <si>
     <t>DASH-VULN-34</t>
@@ -1824,7 +1824,7 @@
     <t>Verify Dashboard screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.258Z</t>
+    <t>2026-07-25T16:00:22.583Z</t>
   </si>
   <si>
     <t>DASH-VULN-35</t>
@@ -1833,7 +1833,7 @@
     <t>Verify Dashboard screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.287Z</t>
+    <t>2026-07-25T16:00:22.605Z</t>
   </si>
   <si>
     <t>DASH-VULN-36</t>
@@ -1842,7 +1842,7 @@
     <t>Verify Dashboard screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.314Z</t>
+    <t>2026-07-25T16:00:22.629Z</t>
   </si>
   <si>
     <t>VOL-VULN-01</t>
@@ -1851,7 +1851,7 @@
     <t>Verify Volunteers screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.346Z</t>
+    <t>2026-07-25T16:00:22.651Z</t>
   </si>
   <si>
     <t>VOL-VULN-02</t>
@@ -1860,7 +1860,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.380Z</t>
+    <t>2026-07-25T16:00:22.675Z</t>
   </si>
   <si>
     <t>VOL-VULN-03</t>
@@ -1869,7 +1869,7 @@
     <t>Verify Volunteers screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.412Z</t>
+    <t>2026-07-25T16:00:22.699Z</t>
   </si>
   <si>
     <t>VOL-VULN-04</t>
@@ -1878,7 +1878,7 @@
     <t>Verify Volunteers screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.441Z</t>
+    <t>2026-07-25T16:00:22.722Z</t>
   </si>
   <si>
     <t>VOL-VULN-05</t>
@@ -1887,7 +1887,7 @@
     <t>Verify Volunteers screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.472Z</t>
+    <t>2026-07-25T16:00:22.743Z</t>
   </si>
   <si>
     <t>VOL-VULN-06</t>
@@ -1896,7 +1896,7 @@
     <t>Verify Volunteers screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.505Z</t>
+    <t>2026-07-25T16:00:22.766Z</t>
   </si>
   <si>
     <t>VOL-VULN-07</t>
@@ -1905,7 +1905,7 @@
     <t>Verify Volunteers screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.544Z</t>
+    <t>2026-07-25T16:00:22.793Z</t>
   </si>
   <si>
     <t>VOL-VULN-08</t>
@@ -1920,7 +1920,7 @@
     <t>Direct access allowed via profile table query bypass</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.586Z</t>
+    <t>2026-07-25T16:00:22.820Z</t>
   </si>
   <si>
     <t>VOL-VULN-09</t>
@@ -1929,7 +1929,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.619Z</t>
+    <t>2026-07-25T16:00:22.845Z</t>
   </si>
   <si>
     <t>VOL-VULN-10</t>
@@ -1938,7 +1938,7 @@
     <t>Verify Volunteers screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.658Z</t>
+    <t>2026-07-25T16:00:22.866Z</t>
   </si>
   <si>
     <t>VOL-VULN-11</t>
@@ -1947,7 +1947,7 @@
     <t>Verify Volunteers screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.699Z</t>
+    <t>2026-07-25T16:00:22.895Z</t>
   </si>
   <si>
     <t>VOL-VULN-12</t>
@@ -1956,7 +1956,7 @@
     <t>Verify Volunteers screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.732Z</t>
+    <t>2026-07-25T16:00:22.923Z</t>
   </si>
   <si>
     <t>VOL-VULN-13</t>
@@ -1965,7 +1965,7 @@
     <t>Verify Volunteers screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.765Z</t>
+    <t>2026-07-25T16:00:22.948Z</t>
   </si>
   <si>
     <t>VOL-VULN-14</t>
@@ -1974,7 +1974,7 @@
     <t>Verify Volunteers screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.796Z</t>
+    <t>2026-07-25T16:00:22.975Z</t>
   </si>
   <si>
     <t>VOL-VULN-15</t>
@@ -1983,7 +1983,7 @@
     <t>Verify Volunteers screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.843Z</t>
+    <t>2026-07-25T16:00:23.000Z</t>
   </si>
   <si>
     <t>VOL-VULN-16</t>
@@ -1992,7 +1992,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.888Z</t>
+    <t>2026-07-25T16:00:23.024Z</t>
   </si>
   <si>
     <t>VOL-VULN-17</t>
@@ -2001,7 +2001,7 @@
     <t>Verify Volunteers screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.937Z</t>
+    <t>2026-07-25T16:00:23.050Z</t>
   </si>
   <si>
     <t>VOL-VULN-18</t>
@@ -2010,7 +2010,7 @@
     <t>Verify Volunteers screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:33.981Z</t>
+    <t>2026-07-25T16:00:23.077Z</t>
   </si>
   <si>
     <t>VOL-VULN-19</t>
@@ -2019,7 +2019,7 @@
     <t>Verify Volunteers screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.016Z</t>
+    <t>2026-07-25T16:00:23.105Z</t>
   </si>
   <si>
     <t>VOL-VULN-20</t>
@@ -2028,7 +2028,7 @@
     <t>Verify Volunteers screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.079Z</t>
+    <t>2026-07-25T16:00:23.127Z</t>
   </si>
   <si>
     <t>VOL-VULN-21</t>
@@ -2037,7 +2037,7 @@
     <t>Verify Volunteers screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.129Z</t>
+    <t>2026-07-25T16:00:23.153Z</t>
   </si>
   <si>
     <t>VOL-VULN-22</t>
@@ -2046,7 +2046,7 @@
     <t>Verify Volunteers screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.161Z</t>
+    <t>2026-07-25T16:00:23.181Z</t>
   </si>
   <si>
     <t>VOL-VULN-23</t>
@@ -2055,7 +2055,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.191Z</t>
+    <t>2026-07-25T16:00:23.207Z</t>
   </si>
   <si>
     <t>VOL-VULN-24</t>
@@ -2064,7 +2064,7 @@
     <t>Verify Volunteers screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.225Z</t>
+    <t>2026-07-25T16:00:23.236Z</t>
   </si>
   <si>
     <t>VOL-VULN-25</t>
@@ -2073,7 +2073,7 @@
     <t>Verify Volunteers screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.262Z</t>
+    <t>2026-07-25T16:00:23.262Z</t>
   </si>
   <si>
     <t>VOL-VULN-26</t>
@@ -2082,7 +2082,7 @@
     <t>Verify Volunteers screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.296Z</t>
+    <t>2026-07-25T16:00:23.297Z</t>
   </si>
   <si>
     <t>VOL-VULN-27</t>
@@ -2091,7 +2091,7 @@
     <t>Verify Volunteers screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.337Z</t>
+    <t>2026-07-25T16:00:23.322Z</t>
   </si>
   <si>
     <t>VOL-VULN-28</t>
@@ -2100,7 +2100,7 @@
     <t>Verify Volunteers screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.393Z</t>
+    <t>2026-07-25T16:00:23.347Z</t>
   </si>
   <si>
     <t>VOL-VULN-29</t>
@@ -2109,7 +2109,7 @@
     <t>Verify Volunteers screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.449Z</t>
+    <t>2026-07-25T16:00:23.373Z</t>
   </si>
   <si>
     <t>VOL-VULN-30</t>
@@ -2118,7 +2118,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.511Z</t>
+    <t>2026-07-25T16:00:23.397Z</t>
   </si>
   <si>
     <t>VOL-VULN-31</t>
@@ -2127,7 +2127,7 @@
     <t>Verify Volunteers screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.554Z</t>
+    <t>2026-07-25T16:00:23.422Z</t>
   </si>
   <si>
     <t>VOL-VULN-32</t>
@@ -2136,7 +2136,7 @@
     <t>Verify Volunteers screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.590Z</t>
+    <t>2026-07-25T16:00:23.451Z</t>
   </si>
   <si>
     <t>VOL-VULN-33</t>
@@ -2145,7 +2145,7 @@
     <t>Verify Volunteers screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.630Z</t>
+    <t>2026-07-25T16:00:23.483Z</t>
   </si>
   <si>
     <t>VOL-VULN-34</t>
@@ -2154,7 +2154,7 @@
     <t>Verify Volunteers screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.684Z</t>
+    <t>2026-07-25T16:00:23.510Z</t>
   </si>
   <si>
     <t>VOL-VULN-35</t>
@@ -2163,7 +2163,7 @@
     <t>Verify Volunteers screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.721Z</t>
+    <t>2026-07-25T16:00:23.551Z</t>
   </si>
   <si>
     <t>VOL-VULN-36</t>
@@ -2172,7 +2172,7 @@
     <t>Verify Volunteers screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.759Z</t>
+    <t>2026-07-25T16:00:23.581Z</t>
   </si>
   <si>
     <t>VOL-VULN-37</t>
@@ -2181,7 +2181,7 @@
     <t>Verify Volunteers screen against Data Exposure vulnerabilities (Case #37)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.800Z</t>
+    <t>2026-07-25T16:00:23.607Z</t>
   </si>
   <si>
     <t>EVT-VULN-01</t>
@@ -2190,7 +2190,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.851Z</t>
+    <t>2026-07-25T16:00:23.637Z</t>
   </si>
   <si>
     <t>EVT-VULN-02</t>
@@ -2199,7 +2199,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.902Z</t>
+    <t>2026-07-25T16:00:23.665Z</t>
   </si>
   <si>
     <t>EVT-VULN-03</t>
@@ -2208,7 +2208,7 @@
     <t>Verify Events screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:34.954Z</t>
+    <t>2026-07-25T16:00:23.692Z</t>
   </si>
   <si>
     <t>EVT-VULN-04</t>
@@ -2217,7 +2217,7 @@
     <t>Verify Events screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.011Z</t>
+    <t>2026-07-25T16:00:23.725Z</t>
   </si>
   <si>
     <t>EVT-VULN-05</t>
@@ -2226,7 +2226,7 @@
     <t>Verify Events screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.056Z</t>
+    <t>2026-07-25T16:00:23.753Z</t>
   </si>
   <si>
     <t>EVT-VULN-06</t>
@@ -2235,7 +2235,7 @@
     <t>Verify Events screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.111Z</t>
+    <t>2026-07-25T16:00:23.779Z</t>
   </si>
   <si>
     <t>EVT-VULN-07</t>
@@ -2244,7 +2244,7 @@
     <t>Verify Events screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.164Z</t>
+    <t>2026-07-25T16:00:23.807Z</t>
   </si>
   <si>
     <t>EVT-VULN-08</t>
@@ -2253,7 +2253,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.213Z</t>
+    <t>2026-07-25T16:00:23.832Z</t>
   </si>
   <si>
     <t>EVT-VULN-09</t>
@@ -2262,7 +2262,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.265Z</t>
+    <t>2026-07-25T16:00:23.859Z</t>
   </si>
   <si>
     <t>EVT-VULN-10</t>
@@ -2271,7 +2271,7 @@
     <t>Verify Events screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.306Z</t>
+    <t>2026-07-25T16:00:23.887Z</t>
   </si>
   <si>
     <t>EVT-VULN-11</t>
@@ -2280,7 +2280,7 @@
     <t>Verify Events screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.368Z</t>
+    <t>2026-07-25T16:00:23.916Z</t>
   </si>
   <si>
     <t>EVT-VULN-12</t>
@@ -2289,7 +2289,7 @@
     <t>Verify Events screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.426Z</t>
+    <t>2026-07-25T16:00:23.970Z</t>
   </si>
   <si>
     <t>EVT-VULN-13</t>
@@ -2298,7 +2298,7 @@
     <t>Verify Events screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.490Z</t>
+    <t>2026-07-25T16:00:24.000Z</t>
   </si>
   <si>
     <t>EVT-VULN-14</t>
@@ -2307,7 +2307,7 @@
     <t>Verify Events screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.542Z</t>
+    <t>2026-07-25T16:00:24.028Z</t>
   </si>
   <si>
     <t>EVT-VULN-15</t>
@@ -2316,7 +2316,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.592Z</t>
+    <t>2026-07-25T16:00:24.062Z</t>
   </si>
   <si>
     <t>EVT-VULN-16</t>
@@ -2325,7 +2325,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.655Z</t>
+    <t>2026-07-25T16:00:24.093Z</t>
   </si>
   <si>
     <t>EVT-VULN-17</t>
@@ -2334,7 +2334,7 @@
     <t>Verify Events screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.721Z</t>
+    <t>2026-07-25T16:00:24.127Z</t>
   </si>
   <si>
     <t>EVT-VULN-18</t>
@@ -2343,7 +2343,7 @@
     <t>Verify Events screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.783Z</t>
+    <t>2026-07-25T16:00:24.159Z</t>
   </si>
   <si>
     <t>EVT-VULN-19</t>
@@ -2352,7 +2352,7 @@
     <t>Verify Events screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.842Z</t>
+    <t>2026-07-25T16:00:24.192Z</t>
   </si>
   <si>
     <t>EVT-VULN-20</t>
@@ -2361,7 +2361,7 @@
     <t>Verify Events screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.896Z</t>
+    <t>2026-07-25T16:00:24.223Z</t>
   </si>
   <si>
     <t>EVT-VULN-21</t>
@@ -2370,7 +2370,7 @@
     <t>Verify Events screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.938Z</t>
+    <t>2026-07-25T16:00:24.256Z</t>
   </si>
   <si>
     <t>EVT-VULN-22</t>
@@ -2379,7 +2379,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:35.977Z</t>
+    <t>2026-07-25T16:00:24.289Z</t>
   </si>
   <si>
     <t>EVT-VULN-23</t>
@@ -2388,7 +2388,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.025Z</t>
+    <t>2026-07-25T16:00:24.325Z</t>
   </si>
   <si>
     <t>EVT-VULN-24</t>
@@ -2397,7 +2397,7 @@
     <t>Verify Events screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.088Z</t>
+    <t>2026-07-25T16:00:24.360Z</t>
   </si>
   <si>
     <t>EVT-VULN-25</t>
@@ -2406,7 +2406,7 @@
     <t>Verify Events screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.147Z</t>
+    <t>2026-07-25T16:00:24.399Z</t>
   </si>
   <si>
     <t>EVT-VULN-26</t>
@@ -2415,7 +2415,7 @@
     <t>Verify Events screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.249Z</t>
+    <t>2026-07-25T16:00:24.426Z</t>
   </si>
   <si>
     <t>EVT-VULN-27</t>
@@ -2424,7 +2424,7 @@
     <t>Verify Events screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.296Z</t>
+    <t>2026-07-25T16:00:24.459Z</t>
   </si>
   <si>
     <t>EVT-VULN-28</t>
@@ -2433,7 +2433,7 @@
     <t>Verify Events screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.331Z</t>
+    <t>2026-07-25T16:00:24.487Z</t>
   </si>
   <si>
     <t>EVT-VULN-29</t>
@@ -2442,7 +2442,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.366Z</t>
+    <t>2026-07-25T16:00:24.516Z</t>
   </si>
   <si>
     <t>EVT-VULN-30</t>
@@ -2451,7 +2451,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.411Z</t>
+    <t>2026-07-25T16:00:24.546Z</t>
   </si>
   <si>
     <t>EVT-VULN-31</t>
@@ -2460,7 +2460,7 @@
     <t>Verify Events screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.457Z</t>
+    <t>2026-07-25T16:00:24.577Z</t>
   </si>
   <si>
     <t>EVT-VULN-32</t>
@@ -2469,7 +2469,7 @@
     <t>Verify Events screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.502Z</t>
+    <t>2026-07-25T16:00:24.607Z</t>
   </si>
   <si>
     <t>EVT-VULN-33</t>
@@ -2478,7 +2478,7 @@
     <t>Verify Events screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.538Z</t>
+    <t>2026-07-25T16:00:24.638Z</t>
   </si>
   <si>
     <t>EVT-VULN-34</t>
@@ -2487,7 +2487,7 @@
     <t>Verify Events screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.575Z</t>
+    <t>2026-07-25T16:00:24.666Z</t>
   </si>
   <si>
     <t>EVT-VULN-35</t>
@@ -2496,7 +2496,7 @@
     <t>Verify Events screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.619Z</t>
+    <t>2026-07-25T16:00:24.694Z</t>
   </si>
   <si>
     <t>EVT-VULN-36</t>
@@ -2505,7 +2505,7 @@
     <t>Verify Events screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.658Z</t>
+    <t>2026-07-25T16:00:24.725Z</t>
   </si>
   <si>
     <t>EVT-VULN-37</t>
@@ -2514,7 +2514,7 @@
     <t>Verify Events screen against Data Exposure vulnerabilities (Case #37)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.697Z</t>
+    <t>2026-07-25T16:00:24.757Z</t>
   </si>
   <si>
     <t>ATT-VULN-01</t>
@@ -2523,7 +2523,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.737Z</t>
+    <t>2026-07-25T16:00:24.794Z</t>
   </si>
   <si>
     <t>ATT-VULN-02</t>
@@ -2532,7 +2532,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.781Z</t>
+    <t>2026-07-25T16:00:24.826Z</t>
   </si>
   <si>
     <t>ATT-VULN-03</t>
@@ -2541,7 +2541,7 @@
     <t>Verify Attendance screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.830Z</t>
+    <t>2026-07-25T16:00:24.860Z</t>
   </si>
   <si>
     <t>ATT-VULN-04</t>
@@ -2550,7 +2550,7 @@
     <t>Verify Attendance screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.886Z</t>
+    <t>2026-07-25T16:00:24.912Z</t>
   </si>
   <si>
     <t>ATT-VULN-05</t>
@@ -2559,7 +2559,7 @@
     <t>Verify Attendance screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:36.938Z</t>
+    <t>2026-07-25T16:00:24.946Z</t>
   </si>
   <si>
     <t>ATT-VULN-06</t>
@@ -2568,7 +2568,7 @@
     <t>Verify Attendance screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.010Z</t>
+    <t>2026-07-25T16:00:24.979Z</t>
   </si>
   <si>
     <t>ATT-VULN-07</t>
@@ -2577,7 +2577,7 @@
     <t>Verify Attendance screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.073Z</t>
+    <t>2026-07-25T16:00:25.009Z</t>
   </si>
   <si>
     <t>ATT-VULN-08</t>
@@ -2586,7 +2586,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.125Z</t>
+    <t>2026-07-25T16:00:25.048Z</t>
   </si>
   <si>
     <t>ATT-VULN-09</t>
@@ -2595,7 +2595,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.163Z</t>
+    <t>2026-07-25T16:00:25.081Z</t>
   </si>
   <si>
     <t>ATT-VULN-10</t>
@@ -2604,7 +2604,7 @@
     <t>Verify Attendance screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.219Z</t>
+    <t>2026-07-25T16:00:25.110Z</t>
   </si>
   <si>
     <t>ATT-VULN-11</t>
@@ -2613,7 +2613,7 @@
     <t>Verify Attendance screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.284Z</t>
+    <t>2026-07-25T16:00:25.146Z</t>
   </si>
   <si>
     <t>ATT-VULN-12</t>
@@ -2622,7 +2622,7 @@
     <t>Verify Attendance screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.334Z</t>
+    <t>2026-07-25T16:00:25.178Z</t>
   </si>
   <si>
     <t>ATT-VULN-13</t>
@@ -2631,7 +2631,7 @@
     <t>Verify Attendance screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.388Z</t>
+    <t>2026-07-25T16:00:25.209Z</t>
   </si>
   <si>
     <t>ATT-VULN-14</t>
@@ -2640,7 +2640,7 @@
     <t>Verify Attendance screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.460Z</t>
+    <t>2026-07-25T16:00:25.244Z</t>
   </si>
   <si>
     <t>ATT-VULN-15</t>
@@ -2649,7 +2649,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.540Z</t>
+    <t>2026-07-25T16:00:25.282Z</t>
   </si>
   <si>
     <t>ATT-VULN-16</t>
@@ -2658,7 +2658,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.597Z</t>
+    <t>2026-07-25T16:00:25.317Z</t>
   </si>
   <si>
     <t>ATT-VULN-17</t>
@@ -2667,7 +2667,7 @@
     <t>Verify Attendance screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.662Z</t>
+    <t>2026-07-25T16:00:25.353Z</t>
   </si>
   <si>
     <t>ATT-VULN-18</t>
@@ -2676,7 +2676,7 @@
     <t>Verify Attendance screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.724Z</t>
+    <t>2026-07-25T16:00:25.390Z</t>
   </si>
   <si>
     <t>ATT-VULN-19</t>
@@ -2685,7 +2685,7 @@
     <t>Verify Attendance screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.776Z</t>
+    <t>2026-07-25T16:00:25.423Z</t>
   </si>
   <si>
     <t>ATT-VULN-20</t>
@@ -2694,7 +2694,7 @@
     <t>Verify Attendance screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.845Z</t>
+    <t>2026-07-25T16:00:25.460Z</t>
   </si>
   <si>
     <t>ATT-VULN-21</t>
@@ -2703,7 +2703,7 @@
     <t>Verify Attendance screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.898Z</t>
+    <t>2026-07-25T16:00:25.497Z</t>
   </si>
   <si>
     <t>ATT-VULN-22</t>
@@ -2712,7 +2712,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.943Z</t>
+    <t>2026-07-25T16:00:25.528Z</t>
   </si>
   <si>
     <t>ATT-VULN-23</t>
@@ -2721,7 +2721,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:37.990Z</t>
+    <t>2026-07-25T16:00:25.559Z</t>
   </si>
   <si>
     <t>ATT-VULN-24</t>
@@ -2730,7 +2730,7 @@
     <t>Verify Attendance screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.051Z</t>
+    <t>2026-07-25T16:00:25.601Z</t>
   </si>
   <si>
     <t>ATT-VULN-25</t>
@@ -2739,7 +2739,7 @@
     <t>Verify Attendance screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.108Z</t>
+    <t>2026-07-25T16:00:25.635Z</t>
   </si>
   <si>
     <t>ATT-VULN-26</t>
@@ -2748,7 +2748,7 @@
     <t>Verify Attendance screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.160Z</t>
+    <t>2026-07-25T16:00:25.670Z</t>
   </si>
   <si>
     <t>ATT-VULN-27</t>
@@ -2757,7 +2757,7 @@
     <t>Verify Attendance screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.209Z</t>
+    <t>2026-07-25T16:00:25.704Z</t>
   </si>
   <si>
     <t>ATT-VULN-28</t>
@@ -2766,7 +2766,7 @@
     <t>Verify Attendance screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.255Z</t>
+    <t>2026-07-25T16:00:25.738Z</t>
   </si>
   <si>
     <t>ATT-VULN-29</t>
@@ -2775,7 +2775,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.313Z</t>
+    <t>2026-07-25T16:00:25.771Z</t>
   </si>
   <si>
     <t>ATT-VULN-30</t>
@@ -2784,7 +2784,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.367Z</t>
+    <t>2026-07-25T16:00:25.806Z</t>
   </si>
   <si>
     <t>ATT-VULN-31</t>
@@ -2793,7 +2793,7 @@
     <t>Verify Attendance screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.430Z</t>
+    <t>2026-07-25T16:00:25.839Z</t>
   </si>
   <si>
     <t>ATT-VULN-32</t>
@@ -2802,7 +2802,7 @@
     <t>Verify Attendance screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.478Z</t>
+    <t>2026-07-25T16:00:25.874Z</t>
   </si>
   <si>
     <t>ATT-VULN-33</t>
@@ -2811,7 +2811,7 @@
     <t>Verify Attendance screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.536Z</t>
+    <t>2026-07-25T16:00:25.908Z</t>
   </si>
   <si>
     <t>ATT-VULN-34</t>
@@ -2820,7 +2820,7 @@
     <t>Verify Attendance screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.602Z</t>
+    <t>2026-07-25T16:00:25.945Z</t>
   </si>
   <si>
     <t>ATT-VULN-35</t>
@@ -2829,7 +2829,7 @@
     <t>Verify Attendance screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.657Z</t>
+    <t>2026-07-25T16:00:25.981Z</t>
   </si>
   <si>
     <t>ATT-VULN-36</t>
@@ -2838,7 +2838,7 @@
     <t>Verify Attendance screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.702Z</t>
+    <t>2026-07-25T16:00:26.021Z</t>
   </si>
   <si>
     <t>ATT-VULN-37</t>
@@ -2847,7 +2847,7 @@
     <t>Verify Attendance screen against Data Exposure vulnerabilities (Case #37)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.746Z</t>
+    <t>2026-07-25T16:00:26.055Z</t>
   </si>
   <si>
     <t>REP-VULN-01</t>
@@ -2856,7 +2856,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.807Z</t>
+    <t>2026-07-25T16:00:26.106Z</t>
   </si>
   <si>
     <t>REP-VULN-02</t>
@@ -2865,7 +2865,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.870Z</t>
+    <t>2026-07-25T16:00:26.169Z</t>
   </si>
   <si>
     <t>REP-VULN-03</t>
@@ -2874,7 +2874,7 @@
     <t>Verify Reports screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.941Z</t>
+    <t>2026-07-25T16:00:26.201Z</t>
   </si>
   <si>
     <t>REP-VULN-04</t>
@@ -2883,7 +2883,7 @@
     <t>Verify Reports screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:38.996Z</t>
+    <t>2026-07-25T16:00:26.238Z</t>
   </si>
   <si>
     <t>REP-VULN-05</t>
@@ -2892,7 +2892,7 @@
     <t>Verify Reports screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.048Z</t>
+    <t>2026-07-25T16:00:26.275Z</t>
   </si>
   <si>
     <t>REP-VULN-06</t>
@@ -2901,7 +2901,7 @@
     <t>Verify Reports screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.102Z</t>
+    <t>2026-07-25T16:00:26.310Z</t>
   </si>
   <si>
     <t>REP-VULN-07</t>
@@ -2910,7 +2910,7 @@
     <t>Verify Reports screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.151Z</t>
+    <t>2026-07-25T16:00:26.344Z</t>
   </si>
   <si>
     <t>REP-VULN-08</t>
@@ -2919,7 +2919,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.199Z</t>
+    <t>2026-07-25T16:00:26.379Z</t>
   </si>
   <si>
     <t>REP-VULN-09</t>
@@ -2928,7 +2928,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.241Z</t>
+    <t>2026-07-25T16:00:26.413Z</t>
   </si>
   <si>
     <t>REP-VULN-10</t>
@@ -2937,7 +2937,7 @@
     <t>Verify Reports screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.296Z</t>
+    <t>2026-07-25T16:00:26.451Z</t>
   </si>
   <si>
     <t>REP-VULN-11</t>
@@ -2946,7 +2946,7 @@
     <t>Verify Reports screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.348Z</t>
+    <t>2026-07-25T16:00:26.489Z</t>
   </si>
   <si>
     <t>REP-VULN-12</t>
@@ -2955,7 +2955,7 @@
     <t>Verify Reports screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.400Z</t>
+    <t>2026-07-25T16:00:26.523Z</t>
   </si>
   <si>
     <t>REP-VULN-13</t>
@@ -2964,7 +2964,7 @@
     <t>Verify Reports screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.445Z</t>
+    <t>2026-07-25T16:00:26.560Z</t>
   </si>
   <si>
     <t>REP-VULN-14</t>
@@ -2973,7 +2973,7 @@
     <t>Verify Reports screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.524Z</t>
+    <t>2026-07-25T16:00:26.600Z</t>
   </si>
   <si>
     <t>REP-VULN-15</t>
@@ -2982,7 +2982,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.569Z</t>
+    <t>2026-07-25T16:00:26.635Z</t>
   </si>
   <si>
     <t>REP-VULN-16</t>
@@ -2991,7 +2991,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.618Z</t>
+    <t>2026-07-25T16:00:26.675Z</t>
   </si>
   <si>
     <t>REP-VULN-17</t>
@@ -3000,7 +3000,7 @@
     <t>Verify Reports screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.663Z</t>
+    <t>2026-07-25T16:00:26.711Z</t>
   </si>
   <si>
     <t>REP-VULN-18</t>
@@ -3009,7 +3009,7 @@
     <t>Verify Reports screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.734Z</t>
+    <t>2026-07-25T16:00:26.754Z</t>
   </si>
   <si>
     <t>REP-VULN-19</t>
@@ -3018,7 +3018,7 @@
     <t>Verify Reports screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.798Z</t>
+    <t>2026-07-25T16:00:26.798Z</t>
   </si>
   <si>
     <t>REP-VULN-20</t>
@@ -3027,7 +3027,7 @@
     <t>Verify Reports screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.845Z</t>
+    <t>2026-07-25T16:00:26.841Z</t>
   </si>
   <si>
     <t>REP-VULN-21</t>
@@ -3036,7 +3036,7 @@
     <t>Verify Reports screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.907Z</t>
+    <t>2026-07-25T16:00:26.879Z</t>
   </si>
   <si>
     <t>REP-VULN-22</t>
@@ -3045,7 +3045,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:39.970Z</t>
+    <t>2026-07-25T16:00:26.917Z</t>
   </si>
   <si>
     <t>REP-VULN-23</t>
@@ -3054,7 +3054,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.015Z</t>
+    <t>2026-07-25T16:00:26.958Z</t>
   </si>
   <si>
     <t>REP-VULN-24</t>
@@ -3063,7 +3063,7 @@
     <t>Verify Reports screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.084Z</t>
+    <t>2026-07-25T16:00:27.014Z</t>
   </si>
   <si>
     <t>REP-VULN-25</t>
@@ -3072,7 +3072,7 @@
     <t>Verify Reports screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.129Z</t>
+    <t>2026-07-25T16:00:27.051Z</t>
   </si>
   <si>
     <t>REP-VULN-26</t>
@@ -3081,7 +3081,7 @@
     <t>Verify Reports screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.190Z</t>
+    <t>2026-07-25T16:00:27.091Z</t>
   </si>
   <si>
     <t>REP-VULN-27</t>
@@ -3090,7 +3090,7 @@
     <t>Verify Reports screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.238Z</t>
+    <t>2026-07-25T16:00:27.126Z</t>
   </si>
   <si>
     <t>REP-VULN-28</t>
@@ -3099,7 +3099,7 @@
     <t>Verify Reports screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.303Z</t>
+    <t>2026-07-25T16:00:27.173Z</t>
   </si>
   <si>
     <t>REP-VULN-29</t>
@@ -3108,7 +3108,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.366Z</t>
+    <t>2026-07-25T16:00:27.212Z</t>
   </si>
   <si>
     <t>REP-VULN-30</t>
@@ -3117,7 +3117,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.459Z</t>
+    <t>2026-07-25T16:00:27.257Z</t>
   </si>
   <si>
     <t>REP-VULN-31</t>
@@ -3126,7 +3126,7 @@
     <t>Verify Reports screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.518Z</t>
+    <t>2026-07-25T16:00:27.298Z</t>
   </si>
   <si>
     <t>REP-VULN-32</t>
@@ -3135,7 +3135,7 @@
     <t>Verify Reports screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.567Z</t>
+    <t>2026-07-25T16:00:27.342Z</t>
   </si>
   <si>
     <t>REP-VULN-33</t>
@@ -3144,7 +3144,7 @@
     <t>Verify Reports screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.631Z</t>
+    <t>2026-07-25T16:00:27.386Z</t>
   </si>
   <si>
     <t>REP-VULN-34</t>
@@ -3153,7 +3153,7 @@
     <t>Verify Reports screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.702Z</t>
+    <t>2026-07-25T16:00:27.425Z</t>
   </si>
   <si>
     <t>REP-VULN-35</t>
@@ -3162,7 +3162,7 @@
     <t>Verify Reports screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.755Z</t>
+    <t>2026-07-25T16:00:27.462Z</t>
   </si>
   <si>
     <t>REP-VULN-36</t>
@@ -3171,7 +3171,7 @@
     <t>Verify Reports screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.811Z</t>
+    <t>2026-07-25T16:00:27.510Z</t>
   </si>
   <si>
     <t>REP-VULN-37</t>
@@ -3180,7 +3180,7 @@
     <t>Verify Reports screen against Data Exposure vulnerabilities (Case #37)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.864Z</t>
+    <t>2026-07-25T16:00:27.547Z</t>
   </si>
   <si>
     <t>SET-VULN-01</t>
@@ -3189,7 +3189,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.912Z</t>
+    <t>2026-07-25T16:00:27.603Z</t>
   </si>
   <si>
     <t>SET-VULN-02</t>
@@ -3198,7 +3198,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:40.963Z</t>
+    <t>2026-07-25T16:00:27.642Z</t>
   </si>
   <si>
     <t>SET-VULN-03</t>
@@ -3213,7 +3213,7 @@
     <t>Exceptions printed directly to output stream</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.029Z</t>
+    <t>2026-07-25T16:00:27.685Z</t>
   </si>
   <si>
     <t>SET-VULN-04</t>
@@ -3222,7 +3222,7 @@
     <t>Verify Settings screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.099Z</t>
+    <t>2026-07-25T16:00:27.724Z</t>
   </si>
   <si>
     <t>SET-VULN-05</t>
@@ -3231,7 +3231,7 @@
     <t>Verify Settings screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.170Z</t>
+    <t>2026-07-25T16:00:27.763Z</t>
   </si>
   <si>
     <t>SET-VULN-06</t>
@@ -3240,7 +3240,7 @@
     <t>Verify Settings screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.222Z</t>
+    <t>2026-07-25T16:00:27.803Z</t>
   </si>
   <si>
     <t>SET-VULN-07</t>
@@ -3249,7 +3249,7 @@
     <t>Verify Settings screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.274Z</t>
+    <t>2026-07-25T16:00:27.839Z</t>
   </si>
   <si>
     <t>SET-VULN-08</t>
@@ -3258,7 +3258,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.332Z</t>
+    <t>2026-07-25T16:00:27.878Z</t>
   </si>
   <si>
     <t>SET-VULN-09</t>
@@ -3267,7 +3267,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.407Z</t>
+    <t>2026-07-25T16:00:27.919Z</t>
   </si>
   <si>
     <t>SET-VULN-10</t>
@@ -3276,7 +3276,7 @@
     <t>Verify Settings screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.468Z</t>
+    <t>2026-07-25T16:00:27.957Z</t>
   </si>
   <si>
     <t>SET-VULN-11</t>
@@ -3285,7 +3285,7 @@
     <t>Verify Settings screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.520Z</t>
+    <t>2026-07-25T16:00:28.002Z</t>
   </si>
   <si>
     <t>SET-VULN-12</t>
@@ -3294,7 +3294,7 @@
     <t>Verify Settings screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.583Z</t>
+    <t>2026-07-25T16:00:28.038Z</t>
   </si>
   <si>
     <t>SET-VULN-13</t>
@@ -3303,7 +3303,7 @@
     <t>Verify Settings screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.671Z</t>
+    <t>2026-07-25T16:00:28.092Z</t>
   </si>
   <si>
     <t>SET-VULN-14</t>
@@ -3312,7 +3312,7 @@
     <t>Verify Settings screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.743Z</t>
+    <t>2026-07-25T16:00:28.132Z</t>
   </si>
   <si>
     <t>SET-VULN-15</t>
@@ -3321,7 +3321,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.806Z</t>
+    <t>2026-07-25T16:00:28.170Z</t>
   </si>
   <si>
     <t>SET-VULN-16</t>
@@ -3330,7 +3330,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.861Z</t>
+    <t>2026-07-25T16:00:28.208Z</t>
   </si>
   <si>
     <t>SET-VULN-17</t>
@@ -3339,7 +3339,7 @@
     <t>Verify Settings screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.935Z</t>
+    <t>2026-07-25T16:00:28.249Z</t>
   </si>
   <si>
     <t>SET-VULN-18</t>
@@ -3348,7 +3348,7 @@
     <t>Verify Settings screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:41.986Z</t>
+    <t>2026-07-25T16:00:28.292Z</t>
   </si>
   <si>
     <t>SET-VULN-19</t>
@@ -3357,7 +3357,7 @@
     <t>Verify Settings screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.056Z</t>
+    <t>2026-07-25T16:00:28.331Z</t>
   </si>
   <si>
     <t>SET-VULN-20</t>
@@ -3366,7 +3366,7 @@
     <t>Verify Settings screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.113Z</t>
+    <t>2026-07-25T16:00:28.365Z</t>
   </si>
   <si>
     <t>SET-VULN-21</t>
@@ -3375,7 +3375,7 @@
     <t>Verify Settings screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.170Z</t>
+    <t>2026-07-25T16:00:28.413Z</t>
   </si>
   <si>
     <t>SET-VULN-22</t>
@@ -3384,7 +3384,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.224Z</t>
+    <t>2026-07-25T16:00:28.458Z</t>
   </si>
   <si>
     <t>SET-VULN-23</t>
@@ -3393,7 +3393,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.292Z</t>
+    <t>2026-07-25T16:00:28.500Z</t>
   </si>
   <si>
     <t>SET-VULN-24</t>
@@ -3402,7 +3402,7 @@
     <t>Verify Settings screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.358Z</t>
+    <t>2026-07-25T16:00:28.540Z</t>
   </si>
   <si>
     <t>SET-VULN-25</t>
@@ -3411,7 +3411,7 @@
     <t>Verify Settings screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.457Z</t>
+    <t>2026-07-25T16:00:28.584Z</t>
   </si>
   <si>
     <t>SET-VULN-26</t>
@@ -3420,7 +3420,7 @@
     <t>Verify Settings screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.519Z</t>
+    <t>2026-07-25T16:00:28.624Z</t>
   </si>
   <si>
     <t>SET-VULN-27</t>
@@ -3429,7 +3429,7 @@
     <t>Verify Settings screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.578Z</t>
+    <t>2026-07-25T16:00:28.674Z</t>
   </si>
   <si>
     <t>SET-VULN-28</t>
@@ -3438,7 +3438,7 @@
     <t>Verify Settings screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.660Z</t>
+    <t>2026-07-25T16:00:28.712Z</t>
   </si>
   <si>
     <t>SET-VULN-29</t>
@@ -3447,7 +3447,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.727Z</t>
+    <t>2026-07-25T16:00:28.751Z</t>
   </si>
   <si>
     <t>SET-VULN-30</t>
@@ -3456,7 +3456,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.780Z</t>
+    <t>2026-07-25T16:00:28.801Z</t>
   </si>
   <si>
     <t>SET-VULN-31</t>
@@ -3465,7 +3465,7 @@
     <t>Verify Settings screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.840Z</t>
+    <t>2026-07-25T16:00:28.851Z</t>
   </si>
   <si>
     <t>SET-VULN-32</t>
@@ -3474,7 +3474,7 @@
     <t>Verify Settings screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.916Z</t>
+    <t>2026-07-25T16:00:28.889Z</t>
   </si>
   <si>
     <t>SET-VULN-33</t>
@@ -3483,7 +3483,7 @@
     <t>Verify Settings screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:42.998Z</t>
+    <t>2026-07-25T16:00:28.931Z</t>
   </si>
   <si>
     <t>SET-VULN-34</t>
@@ -3492,7 +3492,7 @@
     <t>Verify Settings screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.058Z</t>
+    <t>2026-07-25T16:00:28.975Z</t>
   </si>
   <si>
     <t>SET-VULN-35</t>
@@ -3501,7 +3501,7 @@
     <t>Verify Settings screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.122Z</t>
+    <t>2026-07-25T16:00:29.029Z</t>
   </si>
   <si>
     <t>SET-VULN-36</t>
@@ -3510,7 +3510,7 @@
     <t>Verify Settings screen against Broken Auth vulnerabilities (Case #36)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.188Z</t>
+    <t>2026-07-25T16:00:29.071Z</t>
   </si>
   <si>
     <t>SET-VULN-37</t>
@@ -3519,7 +3519,7 @@
     <t>Verify Settings screen against Data Exposure vulnerabilities (Case #37)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.254Z</t>
+    <t>2026-07-25T16:00:29.115Z</t>
   </si>
   <si>
     <t>AI-VULN-01</t>
@@ -3528,7 +3528,7 @@
     <t>Verify AIChat screen against Broken Auth vulnerabilities (Case #1)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.313Z</t>
+    <t>2026-07-25T16:00:29.160Z</t>
   </si>
   <si>
     <t>AI-VULN-02</t>
@@ -3537,7 +3537,7 @@
     <t>Verify AIChat screen against Data Exposure vulnerabilities (Case #2)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.372Z</t>
+    <t>2026-07-25T16:00:29.203Z</t>
   </si>
   <si>
     <t>AI-VULN-03</t>
@@ -3546,7 +3546,7 @@
     <t>Verify AIChat screen against Access Control vulnerabilities (Case #3)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.441Z</t>
+    <t>2026-07-25T16:00:29.244Z</t>
   </si>
   <si>
     <t>AI-VULN-04</t>
@@ -3555,7 +3555,7 @@
     <t>Verify AIChat screen against Config Error vulnerabilities (Case #4)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.525Z</t>
+    <t>2026-07-25T16:00:29.294Z</t>
   </si>
   <si>
     <t>AI-VULN-05</t>
@@ -3564,7 +3564,7 @@
     <t>Verify AIChat screen against Rate Limiting vulnerabilities (Case #5)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.585Z</t>
+    <t>2026-07-25T16:00:29.338Z</t>
   </si>
   <si>
     <t>AI-VULN-06</t>
@@ -3573,7 +3573,7 @@
     <t>Verify AIChat screen against Client Logic vulnerabilities (Case #6)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.670Z</t>
+    <t>2026-07-25T16:00:29.382Z</t>
   </si>
   <si>
     <t>AI-VULN-07</t>
@@ -3582,7 +3582,7 @@
     <t>Verify AIChat screen against Injection vulnerabilities (Case #7)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.721Z</t>
+    <t>2026-07-25T16:00:29.429Z</t>
   </si>
   <si>
     <t>AI-VULN-08</t>
@@ -3591,7 +3591,7 @@
     <t>Verify AIChat screen against Broken Auth vulnerabilities (Case #8)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.789Z</t>
+    <t>2026-07-25T16:00:29.507Z</t>
   </si>
   <si>
     <t>AI-VULN-09</t>
@@ -3600,7 +3600,7 @@
     <t>Verify AIChat screen against Data Exposure vulnerabilities (Case #9)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.862Z</t>
+    <t>2026-07-25T16:00:29.555Z</t>
   </si>
   <si>
     <t>AI-VULN-10</t>
@@ -3609,7 +3609,7 @@
     <t>Verify AIChat screen against Access Control vulnerabilities (Case #10)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:43.934Z</t>
+    <t>2026-07-25T16:00:29.599Z</t>
   </si>
   <si>
     <t>AI-VULN-11</t>
@@ -3618,7 +3618,7 @@
     <t>Verify AIChat screen against Config Error vulnerabilities (Case #11)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.004Z</t>
+    <t>2026-07-25T16:00:29.644Z</t>
   </si>
   <si>
     <t>AI-VULN-12</t>
@@ -3627,7 +3627,7 @@
     <t>Verify AIChat screen against Rate Limiting vulnerabilities (Case #12)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.078Z</t>
+    <t>2026-07-25T16:00:29.691Z</t>
   </si>
   <si>
     <t>AI-VULN-13</t>
@@ -3636,7 +3636,7 @@
     <t>Verify AIChat screen against Client Logic vulnerabilities (Case #13)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.136Z</t>
+    <t>2026-07-25T16:00:29.736Z</t>
   </si>
   <si>
     <t>AI-VULN-14</t>
@@ -3645,7 +3645,7 @@
     <t>Verify AIChat screen against Injection vulnerabilities (Case #14)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.202Z</t>
+    <t>2026-07-25T16:00:29.779Z</t>
   </si>
   <si>
     <t>AI-VULN-15</t>
@@ -3654,7 +3654,7 @@
     <t>Verify AIChat screen against Broken Auth vulnerabilities (Case #15)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.266Z</t>
+    <t>2026-07-25T16:00:29.826Z</t>
   </si>
   <si>
     <t>AI-VULN-16</t>
@@ -3663,7 +3663,7 @@
     <t>Verify AIChat screen against Data Exposure vulnerabilities (Case #16)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.350Z</t>
+    <t>2026-07-25T16:00:29.873Z</t>
   </si>
   <si>
     <t>AI-VULN-17</t>
@@ -3672,7 +3672,7 @@
     <t>Verify AIChat screen against Access Control vulnerabilities (Case #17)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.412Z</t>
+    <t>2026-07-25T16:00:29.919Z</t>
   </si>
   <si>
     <t>AI-VULN-18</t>
@@ -3681,7 +3681,7 @@
     <t>Verify AIChat screen against Config Error vulnerabilities (Case #18)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.473Z</t>
+    <t>2026-07-25T16:00:29.965Z</t>
   </si>
   <si>
     <t>AI-VULN-19</t>
@@ -3690,7 +3690,7 @@
     <t>Verify AIChat screen against Rate Limiting vulnerabilities (Case #19)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.530Z</t>
+    <t>2026-07-25T16:00:30.015Z</t>
   </si>
   <si>
     <t>AI-VULN-20</t>
@@ -3699,7 +3699,7 @@
     <t>Verify AIChat screen against Client Logic vulnerabilities (Case #20)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.597Z</t>
+    <t>2026-07-25T16:00:30.065Z</t>
   </si>
   <si>
     <t>AI-VULN-21</t>
@@ -3708,7 +3708,7 @@
     <t>Verify AIChat screen against Injection vulnerabilities (Case #21)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.654Z</t>
+    <t>2026-07-25T16:00:30.113Z</t>
   </si>
   <si>
     <t>AI-VULN-22</t>
@@ -3717,7 +3717,7 @@
     <t>Verify AIChat screen against Broken Auth vulnerabilities (Case #22)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.728Z</t>
+    <t>2026-07-25T16:00:30.164Z</t>
   </si>
   <si>
     <t>AI-VULN-23</t>
@@ -3726,7 +3726,7 @@
     <t>Verify AIChat screen against Data Exposure vulnerabilities (Case #23)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.815Z</t>
+    <t>2026-07-25T16:00:30.214Z</t>
   </si>
   <si>
     <t>AI-VULN-24</t>
@@ -3735,7 +3735,7 @@
     <t>Verify AIChat screen against Access Control vulnerabilities (Case #24)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.878Z</t>
+    <t>2026-07-25T16:00:30.273Z</t>
   </si>
   <si>
     <t>AI-VULN-25</t>
@@ -3744,7 +3744,7 @@
     <t>Verify AIChat screen against Config Error vulnerabilities (Case #25)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:44.940Z</t>
+    <t>2026-07-25T16:00:30.321Z</t>
   </si>
   <si>
     <t>AI-VULN-26</t>
@@ -3753,7 +3753,7 @@
     <t>Verify AIChat screen against Rate Limiting vulnerabilities (Case #26)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.009Z</t>
+    <t>2026-07-25T16:00:30.371Z</t>
   </si>
   <si>
     <t>AI-VULN-27</t>
@@ -3762,7 +3762,7 @@
     <t>Verify AIChat screen against Client Logic vulnerabilities (Case #27)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.096Z</t>
+    <t>2026-07-25T16:00:30.416Z</t>
   </si>
   <si>
     <t>AI-VULN-28</t>
@@ -3771,7 +3771,7 @@
     <t>Verify AIChat screen against Injection vulnerabilities (Case #28)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.178Z</t>
+    <t>2026-07-25T16:00:30.459Z</t>
   </si>
   <si>
     <t>AI-VULN-29</t>
@@ -3780,7 +3780,7 @@
     <t>Verify AIChat screen against Broken Auth vulnerabilities (Case #29)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.241Z</t>
+    <t>2026-07-25T16:00:30.506Z</t>
   </si>
   <si>
     <t>AI-VULN-30</t>
@@ -3789,7 +3789,7 @@
     <t>Verify AIChat screen against Data Exposure vulnerabilities (Case #30)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.322Z</t>
+    <t>2026-07-25T16:00:30.553Z</t>
   </si>
   <si>
     <t>AI-VULN-31</t>
@@ -3798,7 +3798,7 @@
     <t>Verify AIChat screen against Access Control vulnerabilities (Case #31)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.403Z</t>
+    <t>2026-07-25T16:00:30.595Z</t>
   </si>
   <si>
     <t>AI-VULN-32</t>
@@ -3807,7 +3807,7 @@
     <t>Verify AIChat screen against Config Error vulnerabilities (Case #32)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.458Z</t>
+    <t>2026-07-25T16:00:30.639Z</t>
   </si>
   <si>
     <t>AI-VULN-33</t>
@@ -3816,7 +3816,7 @@
     <t>Verify AIChat screen against Rate Limiting vulnerabilities (Case #33)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.518Z</t>
+    <t>2026-07-25T16:00:30.685Z</t>
   </si>
   <si>
     <t>AI-VULN-34</t>
@@ -3825,7 +3825,7 @@
     <t>Verify AIChat screen against Client Logic vulnerabilities (Case #34)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.592Z</t>
+    <t>2026-07-25T16:00:30.731Z</t>
   </si>
   <si>
     <t>AI-VULN-35</t>
@@ -3834,7 +3834,7 @@
     <t>Verify AIChat screen against Injection vulnerabilities (Case #35)</t>
   </si>
   <si>
-    <t>2026-07-23T04:59:45.681Z</t>
+    <t>2026-07-25T16:00:30.782Z</t>
   </si>
 </sst>
 </file>
